--- a/17. Importing Data from external sources/Pdf_solved.xlsx
+++ b/17. Importing Data from external sources/Pdf_solved.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Advance_Excel_BI\17. Importing Data from external sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71802A4C-9394-4999-BC86-9BB938AF259F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878A88BA-EF17-4A3D-8589-4FCE85791369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{51DCA708-93BC-4244-AF40-CA612C475698}"/>
   </bookViews>
